--- a/_Studying(5th_sem)/ElectricalAndSchemotechnicalEngineering/лаб3/лаб3.xlsx
+++ b/_Studying(5th_sem)/ElectricalAndSchemotechnicalEngineering/лаб3/лаб3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\itmo\_Studying(5th_sem)\ElectricalAndSchemotechnicalEngineering\лаб3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1DB4E3-4D43-40CC-A459-3E065CEEFE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DC86F3-0855-4BB4-BBEC-D5B10F49C86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6735" yWindow="8730" windowWidth="18510" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -393,12 +393,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -424,7 +424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.5</v>
       </c>
@@ -452,7 +452,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.75</v>
       </c>
@@ -480,7 +480,7 @@
         <v>2.1666666666666665</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -508,27 +508,27 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
